--- a/snhu_template.xlsx
+++ b/snhu_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomar\source\repos\snhu-assignment-importer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B75EF47-CCF4-49D3-BD07-F19E8C708DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB418A6-2A30-4720-8BC4-42B44ECDD398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13740" yWindow="4110" windowWidth="23895" windowHeight="14895" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13740" yWindow="4110" windowWidth="23895" windowHeight="14895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grades" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
   <si>
     <t>Term</t>
   </si>
@@ -60,6 +60,9 @@
     <t>Grade</t>
   </si>
   <si>
+    <t>CS-405</t>
+  </si>
+  <si>
     <t>Total</t>
   </si>
   <si>
@@ -82,6 +85,30 @@
   </si>
   <si>
     <t>Access code</t>
+  </si>
+  <si>
+    <t>CS-350</t>
+  </si>
+  <si>
+    <t>2026-C5 (Aug-Oct)</t>
+  </si>
+  <si>
+    <t>SNHU</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>Emerging Sys Arch &amp; Tech</t>
+  </si>
+  <si>
+    <t>Secure Coding</t>
+  </si>
+  <si>
+    <t>MAT-243</t>
+  </si>
+  <si>
+    <t>Applied Statistics for STEM</t>
   </si>
 </sst>
 </file>
@@ -163,16 +190,16 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom"/>
@@ -223,18 +250,18 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table3" displayName="Table3" ref="A1:H3" insertRow="1" totalsRowCount="1">
   <autoFilter ref="A1:H2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="8">
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Term" totalsRowLabel="Total" dataDxfId="16" totalsRowDxfId="6">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Term" totalsRowLabel="Total" dataDxfId="16" totalsRowDxfId="4">
       <calculatedColumnFormula>VLOOKUP($B2,CourseData[#Data],2, FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Name" dataDxfId="15" totalsRowDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Name" dataDxfId="15" totalsRowDxfId="3"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Description" dataDxfId="14">
       <calculatedColumnFormula>VLOOKUP($B2,CourseData[#Data],6, FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Module" dataDxfId="13" totalsRowDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Module" dataDxfId="13" totalsRowDxfId="2"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Assignment" dataDxfId="12"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Max" totalsRowFunction="sum" dataDxfId="11" totalsRowDxfId="3"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Max" totalsRowFunction="sum" dataDxfId="11" totalsRowDxfId="1"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Points" totalsRowFunction="sum" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Grade" dataDxfId="9" totalsRowDxfId="2" dataCellStyle="Percent">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Grade" dataDxfId="9" totalsRowDxfId="0" dataCellStyle="Percent">
       <calculatedColumnFormula>IF(ISNUMBER(G2), G2/Data!#REF!, "")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -243,14 +270,14 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="CourseData" displayName="CourseData" ref="A1:J3" insertRow="1" totalsRowCount="1">
-  <autoFilter ref="A1:J2" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="CourseData" displayName="CourseData" ref="A1:J5" totalsRowCount="1">
+  <autoFilter ref="A1:J4" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="10">
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Name" totalsRowLabel="Total"/>
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Term"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Univeristy"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Status" dataDxfId="8" totalsRowDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Credits" totalsRowFunction="sum" dataDxfId="7" totalsRowDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Status" dataDxfId="8" totalsRowDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Credits" totalsRowFunction="sum" dataDxfId="6" totalsRowDxfId="5"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Description"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Instructor"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Instructor email "/>
@@ -630,7 +657,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1">
         <f>SUBTOTAL(109,Table3[Max])</f>
@@ -652,7 +679,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -673,42 +700,101 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
       </c>
       <c r="G1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="1">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
       <c r="H2" s="4"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="E3" s="1">
+        <v>3</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="1">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1">
         <f>SUBTOTAL(109,CourseData[Credits])</f>
-        <v>0</v>
-      </c>
-      <c r="J3">
+        <v>9</v>
+      </c>
+      <c r="J5">
         <f>SUBTOTAL(103,CourseData[Access code])</f>
         <v>0</v>
       </c>
